--- a/Dados/Historico_DY_JMBI11.xlsx
+++ b/Dados/Historico_DY_JMBI11.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Dados/Historico_DY_JMBI11.xlsx
+++ b/Dados/Historico_DY_JMBI11.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25/07/2026*</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -503,11 +503,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>25/06/2026*</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="E3" t="n">
         <v>85</v>

--- a/Dados/Historico_DY_JMBI11.xlsx
+++ b/Dados/Historico_DY_JMBI11.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="D3" t="n">
